--- a/reports/20260507/API_Mask_Aadhar_Card_claude.xlsx
+++ b/reports/20260507/API_Mask_Aadhar_Card_claude.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1757</t>
+          <t>CandidateId=1817</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1769</t>
+          <t>CandidateId=1819</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1773</t>
+          <t>CandidateId=1823</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1775</t>
+          <t>CandidateId=1825</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1777, AadhaarNo=555566667777</t>
+          <t>CandidateId=1827, AadhaarNo=555566667777</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>CandidateId=1779, AadhaarNo=888899990000</t>
+          <t>CandidateId=1829, AadhaarNo=888899990000</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>payload="'; DROP TABLE candidates; --": created cid=1785, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-'; payload='1 OR 1=1': created cid=1787, stored='XXXX- 1=1'; payload="111111111111' UNION SELECT * F": created cid=1789, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-'</t>
+          <t>payload="'; DROP TABLE candidates; --": created cid=1835, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-'; payload='1 OR 1=1': created cid=1837, stored='XXXX- 1=1'; payload="111111111111' UNION SELECT * F": created cid=1839, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-'</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Rejected: status=None, message=''</t>
+          <t>cid=1841, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-X-ipt&gt;', xss_reflected=False</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Rejected: None</t>
+          <t>cid=1843, stored='XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-XXXX-9012', has_html=False</t>
         </is>
       </c>
     </row>
